--- a/data/NIHONBASHI DATA_MAIN.xlsx
+++ b/data/NIHONBASHI DATA_MAIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/amartinez373_gatech_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417782F2-97C2-45B2-9B17-CA8E4141FF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F17AD3A0-C29D-44D8-86BE-77524DCD878D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property Value Estimates" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="154">
   <si>
     <t>Property Value Estimates — Sample Buildings, Nihonbashi District 2</t>
   </si>
@@ -267,6 +267,9 @@
     <t>No match found — verify manually</t>
   </si>
   <si>
+    <t>age estimated</t>
+  </si>
+  <si>
     <t>Resid</t>
   </si>
   <si>
@@ -336,6 +339,9 @@
     <t>convert to Yen</t>
   </si>
   <si>
+    <t>Total Energy Demand mWH</t>
+  </si>
+  <si>
     <t>Envelope upgrade (R-value, U-value, WWR), HVAC replacement, programmatic/FAR changes</t>
   </si>
   <si>
@@ -375,6 +381,18 @@
     <t>Energy Lifecycle Cost W/DER</t>
   </si>
   <si>
+    <t>Grid mWh</t>
+  </si>
+  <si>
+    <t>PV mWh</t>
+  </si>
+  <si>
+    <t>Batteries mWh</t>
+  </si>
+  <si>
+    <t>Total Building Energy Demand</t>
+  </si>
+  <si>
     <t>PER-BUILDING REVITALIZATION COST — 22 Buildings</t>
   </si>
   <si>
@@ -397,6 +415,15 @@
   </si>
   <si>
     <t>Energy Bill W/O DER</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>Batteries</t>
   </si>
   <si>
     <t>Note: TBD = tier not yet determined (3 unmatched buildings, see Building Age &amp; Tier sheet). TBD buildings are excluded from cost totals until a Built Year is entered.</t>
@@ -497,7 +524,7 @@
     <numFmt numFmtId="168" formatCode="_-[$¥-411]* #,##0.00_-;\-[$¥-411]* #,##0.00_-;_-[$¥-411]* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="_-[$¥-411]* #,##0_-;\-[$¥-411]* #,##0_-;_-[$¥-411]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,8 +630,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,8 +723,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1063,6 +1103,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1070,7 +1134,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1249,14 +1313,33 @@
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1358,6 +1441,1678 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Total Est. Property Value (¥M)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Property Value Estimates'!$A$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Office</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Property Value Estimates'!$D$37:$D$41</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>855.5</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2,648.2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>64,747.8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Total Est. Value (¥M)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Property Value Estimates'!$D$39</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0;\(#,##0.0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>64747.755412901868</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F2D-AF49-9EE2-C87B237E9BAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Property Value Estimates'!$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Residence &amp; Commercial Mixed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Property Value Estimates'!$D$37:$D$41</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>855.5</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2,648.2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>64,747.8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Total Est. Value (¥M)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Property Value Estimates'!$D$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0;\(#,##0.0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2648.2232712991172</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F2D-AF49-9EE2-C87B237E9BAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Property Value Estimates'!$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Apartment</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Property Value Estimates'!$D$37:$D$41</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>855.5</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2,648.2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>64,747.8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Total Est. Value (¥M)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Property Value Estimates'!$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0;\(#,##0.0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>855.45389439258565</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9F2D-AF49-9EE2-C87B237E9BAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1842547327"/>
+        <c:axId val="1799446399"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1842547327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1799446399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1799446399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.0;\(#,##0.0\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1842547327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Total Est. Revitalization  Value (¥M)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reconstruct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$D$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Est. Value (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Building Age &amp; Tier'!$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>16463.609995258794</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B34B-1E4E-9F60-E9BAC1CBA170}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$A$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Renovate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$D$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Est. Value (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Building Age &amp; Tier'!$D$44</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>49098.958460969749</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B34B-1E4E-9F60-E9BAC1CBA170}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Maintenance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Building Age &amp; Tier'!$D$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Est. Value (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Building Age &amp; Tier'!$D$45</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0;\(#,##0\);\-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4181.9522908022209</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B34B-1E4E-9F60-E9BAC1CBA170}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1920850943"/>
+        <c:axId val="1920844223"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1920850943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1920844223"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1920844223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="[$¥-411]#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1920850943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Total Revitalization Cost (¥M)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reconstruct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Cost (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revitalization Cost'!$E$40</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$¥-411]* #,##0_-;\-[$¥-411]* #,##0_-;_-[$¥-411]* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1778.8945325825241</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-41DF-5A4A-9FCF-B68163614FE8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Renovate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Cost (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revitalization Cost'!$E$41</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$¥-411]* #,##0_-;\-[$¥-411]* #,##0_-;_-[$¥-411]* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2407.243992983158</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-41DF-5A4A-9FCF-B68163614FE8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Maintenance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revitalization Cost'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Cost (¥M)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revitalization Cost'!$E$42</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$¥-411]* #,##0_-;\-[$¥-411]* #,##0_-;_-[$¥-411]* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>77.563000345386953</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-41DF-5A4A-9FCF-B68163614FE8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1842545087"/>
+        <c:axId val="1893056511"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1842545087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1893056511"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1893056511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="[$¥-411]#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1842545087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1695,7 +3450,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2033,7 +3788,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2374,7 +4129,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2721,7 +4476,365 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1440" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Total Building Energy Demand (mWH)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1440" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EAA1-4740-916B-C212B899F4A4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-EAA1-4740-916B-C212B899F4A4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-EAA1-4740-916B-C212B899F4A4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-2393-2C4D-BA11-B9779B150080}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Graph Examples'!$U$2:$W$2</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Grid</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PV</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Batteries</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graph Examples'!$U$3:$W$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10.767759775601675</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.9092946720320025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.8206087396562567</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2393-2C4D-BA11-B9779B150080}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.76202906045642604"/>
+          <c:y val="0.20037591134441529"/>
+          <c:w val="0.22525907513679433"/>
+          <c:h val="0.62550743657042873"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3192,510 +5305,167 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4200,7 +5970,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4703,7 +6473,1013 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5208,7 +7984,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5711,7 +8487,1657 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916523A3-20CB-90AC-0B0A-EEDF1E4E75E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>172720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7F19B37-5D4A-FF1A-DFCC-9D38A7AB5020}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F15300D-879B-68AC-670A-B9500B67824C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5823,16 +10249,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>412750</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>641350</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5857,10 +10283,46 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57856F55-2B29-ADA1-7915-D1FB592CD5A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6100,30 +10562,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -6132,10 +10594,10 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="107"/>
+      <c r="D4" s="120"/>
     </row>
     <row r="5" spans="1:14" ht="45" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -6144,10 +10606,10 @@
       <c r="B5" s="3">
         <v>2795000</v>
       </c>
-      <c r="C5" s="100" t="s">
+      <c r="C5" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="100"/>
+      <c r="D5" s="114"/>
     </row>
     <row r="6" spans="1:14" ht="45" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -6157,10 +10619,10 @@
         <f>AVERAGE(B5,B7)</f>
         <v>2309000</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="100"/>
+      <c r="D6" s="114"/>
     </row>
     <row r="7" spans="1:14" ht="45" customHeight="1">
       <c r="A7" s="2" t="s">
@@ -6169,10 +10631,10 @@
       <c r="B7" s="3">
         <v>1823000</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="C7" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="100"/>
+      <c r="D7" s="114"/>
     </row>
     <row r="8" spans="1:14" ht="45" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -6182,28 +10644,28 @@
         <f>B5</f>
         <v>2795000</v>
       </c>
-      <c r="C8" s="100" t="s">
+      <c r="C8" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="100"/>
+      <c r="D8" s="114"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="106"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
     </row>
     <row r="11" spans="1:14" ht="26.25" customHeight="1">
       <c r="A11" s="5" t="s">
@@ -6344,11 +10806,11 @@
       </c>
       <c r="M13" s="11">
         <f>VLOOKUP(A13,'Building Age &amp; Tier'!$A$12:$I$33,7,FALSE())</f>
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="N13" s="12" t="str">
         <f>VLOOKUP(A13,'Building Age &amp; Tier'!$A$12:$I$33,9,FALSE())</f>
-        <v>TBD</v>
+        <v>Renovate</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -6446,11 +10908,11 @@
       </c>
       <c r="M15" s="11">
         <f>VLOOKUP(A15,'Building Age &amp; Tier'!$A$12:$I$33,7,FALSE())</f>
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="N15" s="12" t="str">
         <f>VLOOKUP(A15,'Building Age &amp; Tier'!$A$12:$I$33,9,FALSE())</f>
-        <v>TBD</v>
+        <v>Renovate</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -6548,11 +11010,11 @@
       </c>
       <c r="M17" s="11">
         <f>VLOOKUP(A17,'Building Age &amp; Tier'!$A$12:$I$33,7,FALSE())</f>
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="N17" s="12" t="str">
         <f>VLOOKUP(A17,'Building Age &amp; Tier'!$A$12:$I$33,9,FALSE())</f>
-        <v>TBD</v>
+        <v>Renovate</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
@@ -7372,14 +11834,14 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="101" t="s">
+      <c r="A34" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
       <c r="G34" s="13">
         <f>SUM(G12:G33)</f>
         <v>25315.934758509604</v>
@@ -7405,31 +11867,31 @@
       <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="108" t="s">
+      <c r="A35" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="108"/>
-      <c r="K35" s="108"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="108"/>
-      <c r="N35" s="108"/>
+      <c r="B35" s="121"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="121"/>
+      <c r="J35" s="121"/>
+      <c r="K35" s="121"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="106"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1">
       <c r="A38" s="1" t="s">
@@ -7559,256 +12021,241 @@
       </c>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1">
-      <c r="A46" s="108" t="s">
+      <c r="A46" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="108"/>
-      <c r="C46" s="108"/>
-      <c r="D46" s="108"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="108"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="108"/>
-      <c r="L46" s="108"/>
-      <c r="M46" s="108"/>
-      <c r="N46" s="108"/>
+      <c r="B46" s="121"/>
+      <c r="C46" s="121"/>
+      <c r="D46" s="121"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="121"/>
+      <c r="H46" s="121"/>
+      <c r="I46" s="121"/>
+      <c r="J46" s="121"/>
+      <c r="K46" s="121"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
     </row>
     <row r="47" spans="1:14" ht="15" customHeight="1">
-      <c r="A47" s="108" t="s">
+      <c r="A47" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="108"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="108"/>
-      <c r="E47" s="108"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="108"/>
-      <c r="I47" s="108"/>
-      <c r="J47" s="108"/>
-      <c r="K47" s="108"/>
-      <c r="L47" s="108"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="108"/>
+      <c r="B47" s="121"/>
+      <c r="C47" s="121"/>
+      <c r="D47" s="121"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="121"/>
+      <c r="H47" s="121"/>
+      <c r="I47" s="121"/>
+      <c r="J47" s="121"/>
+      <c r="K47" s="121"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
     </row>
     <row r="48" spans="1:14" ht="15" customHeight="1">
-      <c r="A48" s="108" t="s">
+      <c r="A48" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="108"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="108"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="108"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="108"/>
-      <c r="K48" s="108"/>
-      <c r="L48" s="108"/>
-      <c r="M48" s="108"/>
-      <c r="N48" s="108"/>
+      <c r="B48" s="121"/>
+      <c r="C48" s="121"/>
+      <c r="D48" s="121"/>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="121"/>
+      <c r="H48" s="121"/>
+      <c r="I48" s="121"/>
+      <c r="J48" s="121"/>
+      <c r="K48" s="121"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
     </row>
     <row r="49" spans="1:14" ht="15" customHeight="1">
-      <c r="A49" s="108" t="s">
+      <c r="A49" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="108"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="108"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="108"/>
-      <c r="I49" s="108"/>
-      <c r="J49" s="108"/>
-      <c r="K49" s="108"/>
-      <c r="L49" s="108"/>
-      <c r="M49" s="108"/>
-      <c r="N49" s="108"/>
+      <c r="B49" s="121"/>
+      <c r="C49" s="121"/>
+      <c r="D49" s="121"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="121"/>
+      <c r="H49" s="121"/>
+      <c r="I49" s="121"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
     </row>
     <row r="50" spans="1:14" ht="15" customHeight="1">
-      <c r="A50" s="108" t="s">
+      <c r="A50" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="108"/>
-      <c r="C50" s="108"/>
-      <c r="D50" s="108"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="108"/>
-      <c r="I50" s="108"/>
-      <c r="J50" s="108"/>
-      <c r="K50" s="108"/>
-      <c r="L50" s="108"/>
-      <c r="M50" s="108"/>
-      <c r="N50" s="108"/>
+      <c r="B50" s="121"/>
+      <c r="C50" s="121"/>
+      <c r="D50" s="121"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="121"/>
+      <c r="H50" s="121"/>
+      <c r="I50" s="121"/>
+      <c r="J50" s="121"/>
+      <c r="K50" s="121"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
     </row>
     <row r="51" spans="1:14" ht="15" customHeight="1">
-      <c r="A51" s="108" t="s">
+      <c r="A51" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="108"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="108"/>
-      <c r="E51" s="108"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="108"/>
-      <c r="I51" s="108"/>
-      <c r="J51" s="108"/>
-      <c r="K51" s="108"/>
-      <c r="L51" s="108"/>
-      <c r="M51" s="108"/>
-      <c r="N51" s="108"/>
+      <c r="B51" s="121"/>
+      <c r="C51" s="121"/>
+      <c r="D51" s="121"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="121"/>
+      <c r="H51" s="121"/>
+      <c r="I51" s="121"/>
+      <c r="J51" s="121"/>
+      <c r="K51" s="121"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
     </row>
     <row r="52" spans="1:14" ht="15" customHeight="1">
-      <c r="A52" s="108" t="s">
+      <c r="A52" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="108"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="108"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="108"/>
-      <c r="K52" s="108"/>
-      <c r="L52" s="108"/>
-      <c r="M52" s="108"/>
-      <c r="N52" s="108"/>
+      <c r="B52" s="121"/>
+      <c r="C52" s="121"/>
+      <c r="D52" s="121"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="121"/>
+      <c r="H52" s="121"/>
+      <c r="I52" s="121"/>
+      <c r="J52" s="121"/>
+      <c r="K52" s="121"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
     </row>
     <row r="53" spans="1:14" ht="15" customHeight="1">
-      <c r="A53" s="108" t="s">
+      <c r="A53" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="108"/>
-      <c r="C53" s="108"/>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="108"/>
-      <c r="H53" s="108"/>
-      <c r="I53" s="108"/>
-      <c r="J53" s="108"/>
-      <c r="K53" s="108"/>
-      <c r="L53" s="108"/>
-      <c r="M53" s="108"/>
-      <c r="N53" s="108"/>
+      <c r="B53" s="121"/>
+      <c r="C53" s="121"/>
+      <c r="D53" s="121"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="121"/>
+      <c r="H53" s="121"/>
+      <c r="I53" s="121"/>
+      <c r="J53" s="121"/>
+      <c r="K53" s="121"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
-      <c r="A54" s="108" t="s">
+      <c r="A54" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="108"/>
-      <c r="C54" s="108"/>
-      <c r="D54" s="108"/>
-      <c r="E54" s="108"/>
-      <c r="F54" s="108"/>
-      <c r="G54" s="108"/>
-      <c r="H54" s="108"/>
-      <c r="I54" s="108"/>
-      <c r="J54" s="108"/>
-      <c r="K54" s="108"/>
-      <c r="L54" s="108"/>
-      <c r="M54" s="108"/>
-      <c r="N54" s="108"/>
+      <c r="B54" s="121"/>
+      <c r="C54" s="121"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="121"/>
+      <c r="I54" s="121"/>
+      <c r="J54" s="121"/>
+      <c r="K54" s="121"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
-      <c r="A55" s="108" t="s">
+      <c r="A55" s="121" t="s">
         <v>44</v>
       </c>
-      <c r="B55" s="108"/>
-      <c r="C55" s="108"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="108"/>
-      <c r="F55" s="108"/>
-      <c r="G55" s="108"/>
-      <c r="H55" s="108"/>
-      <c r="I55" s="108"/>
-      <c r="J55" s="108"/>
-      <c r="K55" s="108"/>
-      <c r="L55" s="108"/>
-      <c r="M55" s="108"/>
-      <c r="N55" s="108"/>
+      <c r="B55" s="121"/>
+      <c r="C55" s="121"/>
+      <c r="D55" s="121"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="121"/>
+      <c r="H55" s="121"/>
+      <c r="I55" s="121"/>
+      <c r="J55" s="121"/>
+      <c r="K55" s="121"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
     </row>
     <row r="56" spans="1:14" ht="15" customHeight="1">
-      <c r="A56" s="108" t="s">
+      <c r="A56" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="108"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="108"/>
-      <c r="H56" s="108"/>
-      <c r="I56" s="108"/>
-      <c r="J56" s="108"/>
-      <c r="K56" s="108"/>
-      <c r="L56" s="108"/>
-      <c r="M56" s="108"/>
-      <c r="N56" s="108"/>
+      <c r="B56" s="121"/>
+      <c r="C56" s="121"/>
+      <c r="D56" s="121"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="121"/>
+      <c r="H56" s="121"/>
+      <c r="I56" s="121"/>
+      <c r="J56" s="121"/>
+      <c r="K56" s="121"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
     </row>
     <row r="57" spans="1:14" ht="15" customHeight="1">
-      <c r="A57" s="108" t="s">
+      <c r="A57" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="108"/>
-      <c r="C57" s="108"/>
-      <c r="D57" s="108"/>
-      <c r="E57" s="108"/>
-      <c r="F57" s="108"/>
-      <c r="G57" s="108"/>
-      <c r="H57" s="108"/>
-      <c r="I57" s="108"/>
-      <c r="J57" s="108"/>
-      <c r="K57" s="108"/>
-      <c r="L57" s="108"/>
-      <c r="M57" s="108"/>
-      <c r="N57" s="108"/>
+      <c r="B57" s="121"/>
+      <c r="C57" s="121"/>
+      <c r="D57" s="121"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="121"/>
+      <c r="H57" s="121"/>
+      <c r="I57" s="121"/>
+      <c r="J57" s="121"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
-      <c r="A58" s="108" t="s">
+      <c r="A58" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="108"/>
-      <c r="C58" s="108"/>
-      <c r="D58" s="108"/>
-      <c r="E58" s="108"/>
-      <c r="F58" s="108"/>
-      <c r="G58" s="108"/>
-      <c r="H58" s="108"/>
-      <c r="I58" s="108"/>
-      <c r="J58" s="108"/>
-      <c r="K58" s="108"/>
-      <c r="L58" s="108"/>
-      <c r="M58" s="108"/>
-      <c r="N58" s="108"/>
+      <c r="B58" s="121"/>
+      <c r="C58" s="121"/>
+      <c r="D58" s="121"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="121"/>
+      <c r="H58" s="121"/>
+      <c r="I58" s="121"/>
+      <c r="J58" s="121"/>
+      <c r="K58" s="121"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:N35"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="A47:N47"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A49:N49"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A56:N56"/>
     <mergeCell ref="A57:N57"/>
@@ -7818,20 +12265,36 @@
     <mergeCell ref="A52:N52"/>
     <mergeCell ref="A53:N53"/>
     <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:N35"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -7840,27 +12303,27 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="105" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
     </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="106" t="s">
+    <row r="3" spans="1:10" ht="15" customHeight="1">
+      <c r="A3" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
       <c r="G3" s="1" t="s">
         <v>50</v>
       </c>
@@ -7868,7 +12331,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1">
+    <row r="4" spans="1:10" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
@@ -7885,7 +12348,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1">
+    <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
@@ -7903,7 +12366,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1">
+    <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>59</v>
       </c>
@@ -7921,7 +12384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1">
+    <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>62</v>
       </c>
@@ -7936,20 +12399,20 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="106" t="s">
+    <row r="10" spans="1:10" ht="15" customHeight="1">
+      <c r="A10" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="106"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
     </row>
-    <row r="11" spans="1:9" ht="31.5" customHeight="1">
+    <row r="11" spans="1:10" ht="31.5" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -7978,7 +12441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1">
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="2">
         <v>2070</v>
       </c>
@@ -8009,7 +12472,7 @@
         <v>Maintenance</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1">
+    <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="2">
         <v>2563</v>
       </c>
@@ -8024,17 +12487,22 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="20"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="2" t="str">
+      <c r="G13" s="100">
+        <v>1990</v>
+      </c>
+      <c r="H13" s="2">
         <f t="shared" si="0"/>
-        <v>TBD</v>
+        <v>36</v>
       </c>
       <c r="I13" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>TBD</v>
+        <v>Renovate</v>
+      </c>
+      <c r="J13" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1">
+    <row r="14" spans="1:10" ht="15" customHeight="1">
       <c r="A14" s="2">
         <v>3037</v>
       </c>
@@ -8065,7 +12533,7 @@
         <v>Reconstruct</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1">
+    <row r="15" spans="1:10" ht="15" customHeight="1">
       <c r="A15" s="2">
         <v>3042</v>
       </c>
@@ -8080,17 +12548,22 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="20"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="2" t="str">
+      <c r="G15" s="100">
+        <v>1990</v>
+      </c>
+      <c r="H15" s="2">
         <f t="shared" si="0"/>
-        <v>TBD</v>
+        <v>36</v>
       </c>
       <c r="I15" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>TBD</v>
+        <v>Renovate</v>
+      </c>
+      <c r="J15" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1">
+    <row r="16" spans="1:10" ht="15" customHeight="1">
       <c r="A16" s="2">
         <v>3044</v>
       </c>
@@ -8121,7 +12594,7 @@
         <v>Maintenance</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
+    <row r="17" spans="1:10" ht="15" customHeight="1">
       <c r="A17" s="2">
         <v>3065</v>
       </c>
@@ -8136,17 +12609,22 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="20"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="2" t="str">
+      <c r="G17" s="100">
+        <v>1990</v>
+      </c>
+      <c r="H17" s="2">
         <f t="shared" si="0"/>
-        <v>TBD</v>
+        <v>36</v>
       </c>
       <c r="I17" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>TBD</v>
+        <v>Renovate</v>
+      </c>
+      <c r="J17" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1">
+    <row r="18" spans="1:10" ht="15" customHeight="1">
       <c r="A18" s="2">
         <v>3067</v>
       </c>
@@ -8177,7 +12655,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1">
+    <row r="19" spans="1:10" ht="15" customHeight="1">
       <c r="A19" s="2">
         <v>3074</v>
       </c>
@@ -8194,7 +12672,7 @@
         <v>242</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" s="7">
         <v>1998</v>
@@ -8208,7 +12686,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1">
+    <row r="20" spans="1:10" ht="15" customHeight="1">
       <c r="A20" s="2">
         <v>3078</v>
       </c>
@@ -8239,7 +12717,7 @@
         <v>Reconstruct</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1">
+    <row r="21" spans="1:10" ht="15" customHeight="1">
       <c r="A21" s="2">
         <v>3486</v>
       </c>
@@ -8256,7 +12734,7 @@
         <v>259</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" s="7">
         <v>2009</v>
@@ -8270,7 +12748,7 @@
         <v>Maintenance</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1">
+    <row r="22" spans="1:10" ht="15" customHeight="1">
       <c r="A22" s="2">
         <v>3550</v>
       </c>
@@ -8301,7 +12779,7 @@
         <v>Reconstruct</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1">
+    <row r="23" spans="1:10" ht="15" customHeight="1">
       <c r="A23" s="2">
         <v>3552</v>
       </c>
@@ -8318,7 +12796,7 @@
         <v>231</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="7">
         <v>2020</v>
@@ -8332,7 +12810,7 @@
         <v>Maintenance</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1">
+    <row r="24" spans="1:10" ht="15" customHeight="1">
       <c r="A24" s="2">
         <v>3554</v>
       </c>
@@ -8363,7 +12841,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1">
+    <row r="25" spans="1:10" ht="15" customHeight="1">
       <c r="A25" s="2">
         <v>3562</v>
       </c>
@@ -8394,7 +12872,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1">
+    <row r="26" spans="1:10" ht="15" customHeight="1">
       <c r="A26" s="2">
         <v>4050</v>
       </c>
@@ -8425,7 +12903,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1">
+    <row r="27" spans="1:10" ht="15" customHeight="1">
       <c r="A27" s="2">
         <v>4062</v>
       </c>
@@ -8456,7 +12934,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1">
+    <row r="28" spans="1:10" ht="15" customHeight="1">
       <c r="A28" s="2">
         <v>4560</v>
       </c>
@@ -8473,7 +12951,7 @@
         <v>223</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G28" s="7">
         <v>2004</v>
@@ -8487,7 +12965,7 @@
         <v>Maintenance</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1">
+    <row r="29" spans="1:10" ht="15" customHeight="1">
       <c r="A29" s="2">
         <v>4562</v>
       </c>
@@ -8518,7 +12996,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1">
+    <row r="30" spans="1:10" ht="15" customHeight="1">
       <c r="A30" s="2">
         <v>4569</v>
       </c>
@@ -8549,7 +13027,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1">
+    <row r="31" spans="1:10" ht="15" customHeight="1">
       <c r="A31" s="2">
         <v>4571</v>
       </c>
@@ -8580,7 +13058,7 @@
         <v>Renovate</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1">
+    <row r="32" spans="1:10" ht="15" customHeight="1">
       <c r="A32" s="2">
         <v>5039</v>
       </c>
@@ -8644,68 +13122,68 @@
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A36" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="102"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
+      <c r="A36" s="113" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="113"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
     </row>
     <row r="37" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A37" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="102"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="102"/>
+      <c r="A37" s="113" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="113"/>
+      <c r="C37" s="113"/>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="113"/>
     </row>
     <row r="38" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A38" s="102" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="102"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
+      <c r="A38" s="113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="113"/>
+      <c r="C38" s="113"/>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
     </row>
     <row r="39" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A39" s="102" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="102"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="102"/>
-      <c r="I39" s="102"/>
+      <c r="A39" s="113" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="113"/>
+      <c r="C39" s="113"/>
+      <c r="D39" s="113"/>
+      <c r="E39" s="113"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="113"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="113"/>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1">
-      <c r="A41" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="106"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="106"/>
+      <c r="A41" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="119"/>
+      <c r="C41" s="119"/>
+      <c r="D41" s="119"/>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
@@ -8733,7 +13211,7 @@
         <f>SUMIF($I$12:$I$33,A43,'Property Value Estimates'!$G$12:$G$33)</f>
         <v>5890.3792469620003</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="11">
         <f>SUMIF($I$12:$I$33,A43,'Property Value Estimates'!$J$12:$J$33)</f>
         <v>16463.609995258794</v>
       </c>
@@ -8744,15 +13222,15 @@
       </c>
       <c r="B44" s="17">
         <f>COUNTIF($I$12:$I$33,A44)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" s="9">
         <f>SUMIF($I$12:$I$33,A44,'Property Value Estimates'!$G$12:$G$33)</f>
-        <v>14120.467412390599</v>
-      </c>
-      <c r="D44" s="9">
+        <v>17713.347998404402</v>
+      </c>
+      <c r="D44" s="11">
         <f>SUMIF($I$12:$I$33,A44,'Property Value Estimates'!$J$12:$J$33)</f>
-        <v>39183.036771256222</v>
+        <v>49098.958460969749</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1">
@@ -8767,26 +13245,26 @@
         <f>SUMIF($I$12:$I$33,A45,'Property Value Estimates'!$G$12:$G$33)</f>
         <v>1712.2075131432</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="11">
         <f>SUMIF($I$12:$I$33,A45,'Property Value Estimates'!$J$12:$J$33)</f>
         <v>4181.9522908022209</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B46" s="17">
         <f>COUNTIF($I$12:$I$33,A46)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C46" s="9">
         <f>SUMIF($I$12:$I$33,A46,'Property Value Estimates'!$G$12:$G$33)</f>
-        <v>3592.8805860138</v>
+        <v>0</v>
       </c>
       <c r="D46" s="9">
         <f>SUMIF($I$12:$I$33,A46,'Property Value Estimates'!$J$12:$J$33)</f>
-        <v>9915.9216897135284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
@@ -8799,7 +13277,7 @@
       </c>
       <c r="C47" s="13">
         <f>SUM(C43:C46)</f>
-        <v>25315.934758509597</v>
+        <v>25315.934758509604</v>
       </c>
       <c r="D47" s="13">
         <f>SUM(D43:D46)</f>
@@ -8812,64 +13290,59 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A50" s="102" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="102"/>
-      <c r="C50" s="102"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="102"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="102"/>
-      <c r="H50" s="102"/>
-      <c r="I50" s="102"/>
+      <c r="A50" s="113" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="113"/>
+      <c r="C50" s="113"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="113"/>
+      <c r="I50" s="113"/>
     </row>
     <row r="51" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A51" s="102" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="102"/>
-      <c r="C51" s="102"/>
-      <c r="D51" s="102"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="102"/>
-      <c r="H51" s="102"/>
-      <c r="I51" s="102"/>
+      <c r="A51" s="113" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="113"/>
+      <c r="C51" s="113"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="113"/>
+      <c r="F51" s="113"/>
+      <c r="G51" s="113"/>
+      <c r="H51" s="113"/>
+      <c r="I51" s="113"/>
     </row>
     <row r="52" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A52" s="102" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="102"/>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="102"/>
-      <c r="F52" s="102"/>
-      <c r="G52" s="102"/>
-      <c r="H52" s="102"/>
-      <c r="I52" s="102"/>
+      <c r="A52" s="113" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="113"/>
+      <c r="C52" s="113"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="113"/>
+      <c r="F52" s="113"/>
+      <c r="G52" s="113"/>
+      <c r="H52" s="113"/>
+      <c r="I52" s="113"/>
     </row>
     <row r="53" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A53" s="102" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" s="102"/>
-      <c r="C53" s="102"/>
-      <c r="D53" s="102"/>
-      <c r="E53" s="102"/>
-      <c r="F53" s="102"/>
-      <c r="G53" s="102"/>
-      <c r="H53" s="102"/>
-      <c r="I53" s="102"/>
+      <c r="A53" s="113" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="113"/>
+      <c r="C53" s="113"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="113"/>
+      <c r="F53" s="113"/>
+      <c r="G53" s="113"/>
+      <c r="H53" s="113"/>
+      <c r="I53" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A37:I37"/>
     <mergeCell ref="A52:I52"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A38:I38"/>
@@ -8877,15 +13350,21 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:I37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -8906,76 +13385,90 @@
     <col min="17" max="17" width="13.7109375" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A1" s="105" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
+    <row r="1" spans="1:24" ht="15.75" customHeight="1">
+      <c r="A1" s="118" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
     </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1">
-      <c r="A3" s="106" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
+    <row r="3" spans="1:24" ht="15" customHeight="1">
+      <c r="A3" s="119" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="L3" s="42">
+        <v>0.1</v>
+      </c>
+      <c r="M3">
+        <v>0.02</v>
+      </c>
+      <c r="N3" s="101">
+        <f>AVERAGE(L3:M3)</f>
+        <v>6.0000000000000005E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" ht="39.75" customHeight="1">
-      <c r="A4" s="109" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
+    <row r="4" spans="1:24" ht="39.75" customHeight="1">
+      <c r="A4" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
       <c r="E4" s="3">
         <v>302000</v>
       </c>
-      <c r="F4" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
+      <c r="F4" s="114" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:24">
       <c r="N5">
         <v>160.31</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1">
+    <row r="6" spans="1:24" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="31.5" customHeight="1">
+    <row r="7" spans="1:24" ht="31.5" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="25">
         <v>1</v>
@@ -8985,39 +13478,42 @@
         <v>302000</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T7" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="31.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:24" ht="31.5" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" s="26">
         <v>0.45</v>
@@ -9026,13 +13522,16 @@
         <f>$E$4*C8</f>
         <v>135900</v>
       </c>
+      <c r="U8">
+        <v>1264</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" ht="63.95">
+    <row r="9" spans="1:24" ht="63.95">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="26">
         <v>0.15</v>
@@ -9042,40 +13541,52 @@
         <v>45300</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K9" s="47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O9" s="45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q9" s="58" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R9" s="58" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S9" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T9" s="45" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+      <c r="U9" s="105" t="s">
+        <v>111</v>
+      </c>
+      <c r="V9" s="105" t="s">
+        <v>112</v>
+      </c>
+      <c r="W9" s="105" t="s">
+        <v>113</v>
+      </c>
+      <c r="X9" s="105" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:24">
       <c r="J10">
         <v>1264013</v>
       </c>
@@ -9116,20 +13627,32 @@
         <f>2227050 * 160.31</f>
         <v>357018385.5</v>
       </c>
+      <c r="U10">
+        <v>664</v>
+      </c>
+      <c r="V10">
+        <v>364.4</v>
+      </c>
+      <c r="W10">
+        <v>235.6</v>
+      </c>
+      <c r="X10">
+        <v>1264</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="106" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
+    <row r="11" spans="1:24" ht="15" customHeight="1" thickBot="1">
+      <c r="A11" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
     </row>
-    <row r="12" spans="1:20" ht="63.95">
+    <row r="12" spans="1:24" ht="63.95">
       <c r="A12" s="30" t="s">
         <v>14</v>
       </c>
@@ -9140,58 +13663,70 @@
         <v>19</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E12" s="31" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I12" s="33" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K12" s="47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L12" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="N12" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="P12" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q12" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="R12" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="S12" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="T12" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="U12" s="103" t="s">
+        <v>123</v>
+      </c>
+      <c r="V12" s="104" t="s">
+        <v>124</v>
+      </c>
+      <c r="W12" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="X12" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="M12" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="N12" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="O12" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="R12" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="S12" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="T12" s="45" t="s">
-        <v>108</v>
-      </c>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1">
+    <row r="13" spans="1:24" ht="15" customHeight="1">
       <c r="A13" s="34">
         <f>'Property Value Estimates'!A12</f>
         <v>2070</v>
@@ -9268,12 +13803,28 @@
         <f>$S$10*$D13</f>
         <v>7866535.6559643168</v>
       </c>
-      <c r="T13" s="66">
+      <c r="T13" s="64">
         <f>$T$10*$D13</f>
         <v>5789590.6785198078</v>
       </c>
+      <c r="U13" s="107">
+        <f>$U$10*$D13</f>
+        <v>10.767759775601675</v>
+      </c>
+      <c r="V13" s="108">
+        <f>$V$10*$D13</f>
+        <v>5.9092946720320025</v>
+      </c>
+      <c r="W13" s="108">
+        <f>$W$10*$D13</f>
+        <v>3.8206087396562567</v>
+      </c>
+      <c r="X13" s="112">
+        <f>SUM(U13:W13)</f>
+        <v>20.497663187289938</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1">
+    <row r="14" spans="1:24" ht="15" customHeight="1">
       <c r="A14" s="34">
         <f>'Property Value Estimates'!A13</f>
         <v>2563</v>
@@ -9292,23 +13843,23 @@
       </c>
       <c r="E14" s="28" t="str">
         <f>'Property Value Estimates'!N13</f>
-        <v>TBD</v>
-      </c>
-      <c r="F14" s="29" t="str">
+        <v>Renovate</v>
+      </c>
+      <c r="F14" s="29">
         <f t="shared" si="0"/>
-        <v>TBD</v>
-      </c>
-      <c r="G14" s="29" t="str">
+        <v>135900</v>
+      </c>
+      <c r="G14" s="29">
         <f t="shared" si="1"/>
-        <v>TBD</v>
-      </c>
-      <c r="H14" s="27" t="str">
+        <v>11157525.89893998</v>
+      </c>
+      <c r="H14" s="27">
         <f t="shared" si="2"/>
-        <v>TBD</v>
-      </c>
-      <c r="I14" s="36" t="str">
+        <v>11.15752589893998</v>
+      </c>
+      <c r="I14" s="36">
         <f t="shared" si="3"/>
-        <v>TBD</v>
+        <v>135900</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" ref="J14:J35" si="8">$J$10*D14</f>
@@ -9350,12 +13901,28 @@
         <f t="shared" ref="S14:S35" si="14">$S$10*$D14</f>
         <v>1573188.3291344368</v>
       </c>
-      <c r="T14" s="66">
+      <c r="T14" s="64">
         <f t="shared" ref="T14:T35" si="15">$T$10*$D14</f>
         <v>1157830.7001007765</v>
       </c>
+      <c r="U14" s="107">
+        <f t="shared" ref="U14:U35" si="16">$U$10*$D14</f>
+        <v>2.1533893381715368</v>
+      </c>
+      <c r="V14" s="108">
+        <f t="shared" ref="V14:V35" si="17">$V$10*$D14</f>
+        <v>1.1817696910085962</v>
+      </c>
+      <c r="W14" s="108">
+        <f t="shared" ref="W14:X35" si="18">$W$10*$D14</f>
+        <v>0.76406404830303321</v>
+      </c>
+      <c r="X14" s="112">
+        <f t="shared" ref="X14:X35" si="19">SUM(U14:W14)</f>
+        <v>4.0992230774831659</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1">
+    <row r="15" spans="1:24" ht="15" customHeight="1">
       <c r="A15" s="34">
         <f>'Property Value Estimates'!A14</f>
         <v>3037</v>
@@ -9432,12 +13999,28 @@
         <f t="shared" si="14"/>
         <v>68066454.089161739</v>
       </c>
-      <c r="T15" s="66">
+      <c r="T15" s="64">
         <f t="shared" si="15"/>
         <v>50095356.501145795</v>
       </c>
+      <c r="U15" s="107">
+        <f t="shared" si="16"/>
+        <v>93.169758387025169</v>
+      </c>
+      <c r="V15" s="108">
+        <f t="shared" si="17"/>
+        <v>51.131114391915617</v>
+      </c>
+      <c r="W15" s="108">
+        <f t="shared" si="18"/>
+        <v>33.058426319251701</v>
+      </c>
+      <c r="X15" s="112">
+        <f t="shared" si="19"/>
+        <v>177.35929909819251</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1">
+    <row r="16" spans="1:24" ht="15" customHeight="1">
       <c r="A16" s="34">
         <f>'Property Value Estimates'!A15</f>
         <v>3042</v>
@@ -9456,23 +14039,23 @@
       </c>
       <c r="E16" s="28" t="str">
         <f>'Property Value Estimates'!N15</f>
-        <v>TBD</v>
-      </c>
-      <c r="F16" s="29" t="str">
+        <v>Renovate</v>
+      </c>
+      <c r="F16" s="29">
         <f t="shared" si="0"/>
-        <v>TBD</v>
-      </c>
-      <c r="G16" s="29" t="str">
+        <v>135900</v>
+      </c>
+      <c r="G16" s="29">
         <f t="shared" si="1"/>
-        <v>TBD</v>
-      </c>
-      <c r="H16" s="27" t="str">
+        <v>452988931.31066161</v>
+      </c>
+      <c r="H16" s="27">
         <f t="shared" si="2"/>
-        <v>TBD</v>
-      </c>
-      <c r="I16" s="36" t="str">
+        <v>452.9889313106616</v>
+      </c>
+      <c r="I16" s="36">
         <f t="shared" si="3"/>
-        <v>TBD</v>
+        <v>135900</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="8"/>
@@ -9514,12 +14097,28 @@
         <f t="shared" si="14"/>
         <v>63870512.730131142</v>
       </c>
-      <c r="T16" s="66">
+      <c r="T16" s="64">
         <f t="shared" si="15"/>
         <v>47007239.438911319</v>
       </c>
+      <c r="U16" s="107">
+        <f t="shared" si="16"/>
+        <v>87.426329441616716</v>
+      </c>
+      <c r="V16" s="108">
+        <f t="shared" si="17"/>
+        <v>47.979148265851094</v>
+      </c>
+      <c r="W16" s="108">
+        <f t="shared" si="18"/>
+        <v>31.020547012718218</v>
+      </c>
+      <c r="X16" s="112">
+        <f t="shared" si="19"/>
+        <v>166.42602472018604</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" ht="15" customHeight="1">
+    <row r="17" spans="1:24" ht="15" customHeight="1">
       <c r="A17" s="34">
         <f>'Property Value Estimates'!A16</f>
         <v>3044</v>
@@ -9596,12 +14195,28 @@
         <f t="shared" si="14"/>
         <v>10132914.82395263</v>
       </c>
-      <c r="T17" s="66">
+      <c r="T17" s="64">
         <f t="shared" si="15"/>
         <v>7457594.0130026452</v>
       </c>
+      <c r="U17" s="107">
+        <f t="shared" si="16"/>
+        <v>13.869992767175729</v>
+      </c>
+      <c r="V17" s="108">
+        <f t="shared" si="17"/>
+        <v>7.6117851872874027</v>
+      </c>
+      <c r="W17" s="108">
+        <f t="shared" si="18"/>
+        <v>4.9213408071484963</v>
+      </c>
+      <c r="X17" s="112">
+        <f t="shared" si="19"/>
+        <v>26.40311876161163</v>
+      </c>
     </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1">
+    <row r="18" spans="1:24" ht="15" customHeight="1">
       <c r="A18" s="34">
         <f>'Property Value Estimates'!A17</f>
         <v>3065</v>
@@ -9620,23 +14235,23 @@
       </c>
       <c r="E18" s="28" t="str">
         <f>'Property Value Estimates'!N17</f>
-        <v>TBD</v>
-      </c>
-      <c r="F18" s="29" t="str">
+        <v>Renovate</v>
+      </c>
+      <c r="F18" s="29">
         <f t="shared" si="0"/>
-        <v>TBD</v>
-      </c>
-      <c r="G18" s="29" t="str">
+        <v>135900</v>
+      </c>
+      <c r="G18" s="29">
         <f t="shared" si="1"/>
-        <v>TBD</v>
-      </c>
-      <c r="H18" s="27" t="str">
+        <v>24126014.429673839</v>
+      </c>
+      <c r="H18" s="27">
         <f t="shared" si="2"/>
-        <v>TBD</v>
-      </c>
-      <c r="I18" s="36" t="str">
+        <v>24.126014429673841</v>
+      </c>
+      <c r="I18" s="36">
         <f t="shared" si="3"/>
-        <v>TBD</v>
+        <v>135900</v>
       </c>
       <c r="J18" s="43">
         <f t="shared" si="8"/>
@@ -9678,12 +14293,28 @@
         <f t="shared" si="14"/>
         <v>3401718.6850444856</v>
       </c>
-      <c r="T18" s="66">
+      <c r="T18" s="64">
         <f t="shared" si="15"/>
         <v>2503587.3033827823</v>
       </c>
+      <c r="U18" s="107">
+        <f t="shared" si="16"/>
+        <v>4.6562923282452839</v>
+      </c>
+      <c r="V18" s="108">
+        <f t="shared" si="17"/>
+        <v>2.5553507897779841</v>
+      </c>
+      <c r="W18" s="108">
+        <f t="shared" si="18"/>
+        <v>1.6521422779135375</v>
+      </c>
+      <c r="X18" s="112">
+        <f t="shared" si="19"/>
+        <v>8.8637853959368051</v>
+      </c>
     </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1">
+    <row r="19" spans="1:24" ht="15" customHeight="1">
       <c r="A19" s="34">
         <f>'Property Value Estimates'!A18</f>
         <v>3067</v>
@@ -9760,12 +14391,28 @@
         <f t="shared" si="14"/>
         <v>977198.23891517182</v>
       </c>
-      <c r="T19" s="66">
+      <c r="T19" s="64">
         <f t="shared" si="15"/>
         <v>719195.59797580529</v>
       </c>
+      <c r="U19" s="107">
+        <f t="shared" si="16"/>
+        <v>1.3375946350413785</v>
+      </c>
+      <c r="V19" s="108">
+        <f t="shared" si="17"/>
+        <v>0.73406548947150352</v>
+      </c>
+      <c r="W19" s="108">
+        <f t="shared" si="18"/>
+        <v>0.47460436146950119</v>
+      </c>
+      <c r="X19" s="112">
+        <f t="shared" si="19"/>
+        <v>2.5462644859823835</v>
+      </c>
     </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1">
+    <row r="20" spans="1:24" ht="15" customHeight="1">
       <c r="A20" s="34">
         <f>'Property Value Estimates'!A19</f>
         <v>3074</v>
@@ -9842,12 +14489,28 @@
         <f t="shared" si="14"/>
         <v>11184301.526280154</v>
       </c>
-      <c r="T20" s="66">
+      <c r="T20" s="64">
         <f t="shared" si="15"/>
         <v>8231390.6265983563</v>
       </c>
+      <c r="U20" s="107">
+        <f t="shared" si="16"/>
+        <v>15.309137002585286</v>
+      </c>
+      <c r="V20" s="108">
+        <f t="shared" si="17"/>
+        <v>8.4015806080452986</v>
+      </c>
+      <c r="W20" s="108">
+        <f t="shared" si="18"/>
+        <v>5.4319769244112859</v>
+      </c>
+      <c r="X20" s="112">
+        <f t="shared" si="19"/>
+        <v>29.142694535041869</v>
+      </c>
     </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1">
+    <row r="21" spans="1:24" ht="15" customHeight="1">
       <c r="A21" s="34">
         <f>'Property Value Estimates'!A20</f>
         <v>3078</v>
@@ -9924,12 +14587,28 @@
         <f t="shared" si="14"/>
         <v>12187582.067466302</v>
       </c>
-      <c r="T21" s="66">
+      <c r="T21" s="64">
         <f t="shared" si="15"/>
         <v>8969782.2036819272</v>
       </c>
+      <c r="U21" s="107">
+        <f t="shared" si="16"/>
+        <v>16.682433244729353</v>
+      </c>
+      <c r="V21" s="108">
+        <f t="shared" si="17"/>
+        <v>9.1552389674388177</v>
+      </c>
+      <c r="W21" s="108">
+        <f t="shared" si="18"/>
+        <v>5.9192489043045713</v>
+      </c>
+      <c r="X21" s="112">
+        <f t="shared" si="19"/>
+        <v>31.756921116472743</v>
+      </c>
     </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1">
+    <row r="22" spans="1:24" ht="15" customHeight="1">
       <c r="A22" s="34">
         <f>'Property Value Estimates'!A21</f>
         <v>3486</v>
@@ -10006,12 +14685,28 @@
         <f t="shared" si="14"/>
         <v>8991708.2709878944</v>
       </c>
-      <c r="T22" s="66">
+      <c r="T22" s="64">
         <f t="shared" si="15"/>
         <v>6617692.0395969925</v>
       </c>
+      <c r="U22" s="107">
+        <f t="shared" si="16"/>
+        <v>12.307902597616792</v>
+      </c>
+      <c r="V22" s="108">
+        <f t="shared" si="17"/>
+        <v>6.7545176303788539</v>
+      </c>
+      <c r="W22" s="108">
+        <f t="shared" si="18"/>
+        <v>4.3670811024074041</v>
+      </c>
+      <c r="X22" s="112">
+        <f t="shared" si="19"/>
+        <v>23.429501330403049</v>
+      </c>
     </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1">
+    <row r="23" spans="1:24" ht="15" customHeight="1">
       <c r="A23" s="34">
         <f>'Property Value Estimates'!A22</f>
         <v>3550</v>
@@ -10088,12 +14783,28 @@
         <f t="shared" si="14"/>
         <v>16773899.962471168</v>
       </c>
-      <c r="T23" s="66">
+      <c r="T23" s="64">
         <f t="shared" si="15"/>
         <v>12345207.485523326</v>
       </c>
+      <c r="U23" s="107">
+        <f t="shared" si="16"/>
+        <v>22.9602118638999</v>
+      </c>
+      <c r="V23" s="108">
+        <f t="shared" si="17"/>
+        <v>12.600453619284824</v>
+      </c>
+      <c r="W23" s="108">
+        <f t="shared" si="18"/>
+        <v>8.1467257758054465</v>
+      </c>
+      <c r="X23" s="112">
+        <f t="shared" si="19"/>
+        <v>43.707391258990171</v>
+      </c>
     </row>
-    <row r="24" spans="1:20" ht="15" customHeight="1">
+    <row r="24" spans="1:24" ht="15" customHeight="1">
       <c r="A24" s="34">
         <f>'Property Value Estimates'!A23</f>
         <v>3552</v>
@@ -10170,12 +14881,28 @@
         <f t="shared" si="14"/>
         <v>2094679.536905861</v>
       </c>
-      <c r="T24" s="66">
+      <c r="T24" s="64">
         <f t="shared" si="15"/>
         <v>1541636.3252814538</v>
       </c>
+      <c r="U24" s="107">
+        <f t="shared" si="16"/>
+        <v>2.867209537551632</v>
+      </c>
+      <c r="V24" s="108">
+        <f t="shared" si="17"/>
+        <v>1.5735107763310461</v>
+      </c>
+      <c r="W24" s="108">
+        <f t="shared" si="18"/>
+        <v>1.0173412154324766</v>
+      </c>
+      <c r="X24" s="112">
+        <f t="shared" si="19"/>
+        <v>5.4580615293151542</v>
+      </c>
     </row>
-    <row r="25" spans="1:20" ht="15" customHeight="1">
+    <row r="25" spans="1:24" ht="15" customHeight="1">
       <c r="A25" s="34">
         <f>'Property Value Estimates'!A24</f>
         <v>3554</v>
@@ -10252,12 +14979,28 @@
         <f t="shared" si="14"/>
         <v>41171619.943248987</v>
       </c>
-      <c r="T25" s="66">
+      <c r="T25" s="64">
         <f t="shared" si="15"/>
         <v>30301372.480561703</v>
       </c>
+      <c r="U25" s="107">
+        <f t="shared" si="16"/>
+        <v>56.355952926387793</v>
+      </c>
+      <c r="V25" s="108">
+        <f t="shared" si="17"/>
+        <v>30.927875371047758</v>
+      </c>
+      <c r="W25" s="108">
+        <f t="shared" si="18"/>
+        <v>19.996178478097839</v>
+      </c>
+      <c r="X25" s="112">
+        <f t="shared" si="19"/>
+        <v>107.28000677553339</v>
+      </c>
     </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1">
+    <row r="26" spans="1:24" ht="15" customHeight="1">
       <c r="A26" s="34">
         <f>'Property Value Estimates'!A25</f>
         <v>3562</v>
@@ -10334,12 +15077,28 @@
         <f t="shared" si="14"/>
         <v>34071999.438071303</v>
       </c>
-      <c r="T26" s="66">
+      <c r="T26" s="64">
         <f t="shared" si="15"/>
         <v>25076213.847149763</v>
       </c>
+      <c r="U26" s="107">
+        <f t="shared" si="16"/>
+        <v>46.63795107131098</v>
+      </c>
+      <c r="V26" s="108">
+        <f t="shared" si="17"/>
+        <v>25.594682786725482</v>
+      </c>
+      <c r="W26" s="108">
+        <f t="shared" si="18"/>
+        <v>16.548044084941065</v>
+      </c>
+      <c r="X26" s="112">
+        <f t="shared" si="19"/>
+        <v>88.780677942977533</v>
+      </c>
     </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1">
+    <row r="27" spans="1:24" ht="15" customHeight="1">
       <c r="A27" s="34">
         <f>'Property Value Estimates'!A26</f>
         <v>4050</v>
@@ -10416,12 +15175,28 @@
         <f t="shared" si="14"/>
         <v>119396514.08355477</v>
       </c>
-      <c r="T27" s="66">
+      <c r="T27" s="64">
         <f t="shared" si="15"/>
         <v>87873108.979275346</v>
       </c>
+      <c r="U27" s="107">
+        <f t="shared" si="16"/>
+        <v>163.43064316008125</v>
+      </c>
+      <c r="V27" s="108">
+        <f t="shared" si="17"/>
+        <v>89.68994934869518</v>
+      </c>
+      <c r="W27" s="108">
+        <f t="shared" si="18"/>
+        <v>57.988342663426415</v>
+      </c>
+      <c r="X27" s="112">
+        <f t="shared" si="19"/>
+        <v>311.10893517220285</v>
+      </c>
     </row>
-    <row r="28" spans="1:20" ht="15" customHeight="1">
+    <row r="28" spans="1:24" ht="15" customHeight="1">
       <c r="A28" s="34">
         <f>'Property Value Estimates'!A27</f>
         <v>4062</v>
@@ -10498,12 +15273,28 @@
         <f t="shared" si="14"/>
         <v>20367905.525200143</v>
       </c>
-      <c r="T28" s="66">
+      <c r="T28" s="64">
         <f t="shared" si="15"/>
         <v>14990313.541674962</v>
       </c>
+      <c r="U28" s="107">
+        <f t="shared" si="16"/>
+        <v>27.879707589098867</v>
+      </c>
+      <c r="V28" s="108">
+        <f t="shared" si="17"/>
+        <v>15.300249164860883</v>
+      </c>
+      <c r="W28" s="108">
+        <f t="shared" si="18"/>
+        <v>9.892257692758573</v>
+      </c>
+      <c r="X28" s="112">
+        <f t="shared" si="19"/>
+        <v>53.07221444671832</v>
+      </c>
     </row>
-    <row r="29" spans="1:20" ht="15" customHeight="1">
+    <row r="29" spans="1:24" ht="15" customHeight="1">
       <c r="A29" s="34">
         <f>'Property Value Estimates'!A28</f>
         <v>4560</v>
@@ -10580,12 +15371,28 @@
         <f t="shared" si="14"/>
         <v>3722834.8950870428</v>
       </c>
-      <c r="T29" s="66">
+      <c r="T29" s="64">
         <f t="shared" si="15"/>
         <v>2739921.5040641748</v>
       </c>
+      <c r="U29" s="107">
+        <f t="shared" si="16"/>
+        <v>5.095838064895994</v>
+      </c>
+      <c r="V29" s="108">
+        <f t="shared" si="17"/>
+        <v>2.7965713717591867</v>
+      </c>
+      <c r="W29" s="108">
+        <f t="shared" si="18"/>
+        <v>1.8081015784480363</v>
+      </c>
+      <c r="X29" s="112">
+        <f t="shared" si="19"/>
+        <v>9.700511015103217</v>
+      </c>
     </row>
-    <row r="30" spans="1:20" ht="15" customHeight="1">
+    <row r="30" spans="1:24" ht="15" customHeight="1">
       <c r="A30" s="34">
         <f>'Property Value Estimates'!A29</f>
         <v>4562</v>
@@ -10662,12 +15469,28 @@
         <f t="shared" si="14"/>
         <v>6389217.2337956643</v>
       </c>
-      <c r="T30" s="66">
+      <c r="T30" s="64">
         <f t="shared" si="15"/>
         <v>4702318.0415861169</v>
       </c>
+      <c r="U30" s="107">
+        <f t="shared" si="16"/>
+        <v>8.7455977238829945</v>
+      </c>
+      <c r="V30" s="108">
+        <f t="shared" si="17"/>
+        <v>4.799541883408077</v>
+      </c>
+      <c r="W30" s="108">
+        <f t="shared" si="18"/>
+        <v>3.1031066622693277</v>
+      </c>
+      <c r="X30" s="112">
+        <f t="shared" si="19"/>
+        <v>16.648246269560399</v>
+      </c>
     </row>
-    <row r="31" spans="1:20" ht="15" customHeight="1">
+    <row r="31" spans="1:24" ht="15" customHeight="1">
       <c r="A31" s="34">
         <f>'Property Value Estimates'!A30</f>
         <v>4569</v>
@@ -10744,12 +15567,28 @@
         <f t="shared" si="14"/>
         <v>16292524.233495476</v>
       </c>
-      <c r="T31" s="66">
+      <c r="T31" s="64">
         <f t="shared" si="15"/>
         <v>11990925.937046479</v>
       </c>
+      <c r="U31" s="107">
+        <f t="shared" si="16"/>
+        <v>22.301301965298542</v>
+      </c>
+      <c r="V31" s="108">
+        <f t="shared" si="17"/>
+        <v>12.23884704240179</v>
+      </c>
+      <c r="W31" s="108">
+        <f t="shared" si="18"/>
+        <v>7.9129318419041219</v>
+      </c>
+      <c r="X31" s="112">
+        <f t="shared" si="19"/>
+        <v>42.453080849604461</v>
+      </c>
     </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1">
+    <row r="32" spans="1:24" ht="15" customHeight="1">
       <c r="A32" s="34">
         <f>'Property Value Estimates'!A31</f>
         <v>4571</v>
@@ -10826,12 +15665,28 @@
         <f t="shared" si="14"/>
         <v>20719779.048415381</v>
       </c>
-      <c r="T32" s="66">
+      <c r="T32" s="64">
         <f t="shared" si="15"/>
         <v>15249284.422774354</v>
       </c>
+      <c r="U32" s="107">
+        <f t="shared" si="16"/>
+        <v>28.361354114975043</v>
+      </c>
+      <c r="V32" s="108">
+        <f t="shared" si="17"/>
+        <v>15.564574457073652</v>
+      </c>
+      <c r="W32" s="108">
+        <f t="shared" si="18"/>
+        <v>10.063155164891747</v>
+      </c>
+      <c r="X32" s="112">
+        <f t="shared" si="19"/>
+        <v>53.989083736940444</v>
+      </c>
     </row>
-    <row r="33" spans="1:20" ht="15" customHeight="1">
+    <row r="33" spans="1:24" ht="15" customHeight="1">
       <c r="A33" s="34">
         <f>'Property Value Estimates'!A32</f>
         <v>5039</v>
@@ -10908,12 +15763,28 @@
         <f t="shared" si="14"/>
         <v>10236132.780984553</v>
       </c>
-      <c r="T33" s="66">
+      <c r="T33" s="64">
         <f t="shared" si="15"/>
         <v>7533560.0732892705</v>
       </c>
+      <c r="U33" s="107">
+        <f t="shared" si="16"/>
+        <v>14.011278107312139</v>
+      </c>
+      <c r="V33" s="108">
+        <f t="shared" si="17"/>
+        <v>7.6893219010610592</v>
+      </c>
+      <c r="W33" s="108">
+        <f t="shared" si="18"/>
+        <v>4.9714715694017171</v>
+      </c>
+      <c r="X33" s="112">
+        <f t="shared" si="19"/>
+        <v>26.672071577774915</v>
+      </c>
     </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1">
+    <row r="34" spans="1:24" ht="15" customHeight="1">
       <c r="A34" s="34">
         <f>'Property Value Estimates'!A33</f>
         <v>5050</v>
@@ -10990,16 +15861,32 @@
         <f t="shared" si="14"/>
         <v>5605151.7717313273</v>
       </c>
-      <c r="T34" s="66">
+      <c r="T34" s="64">
         <f t="shared" si="15"/>
         <v>4125263.7588568097</v>
       </c>
+      <c r="U34" s="107">
+        <f t="shared" si="16"/>
+        <v>7.6723643574958738</v>
+      </c>
+      <c r="V34" s="108">
+        <f t="shared" si="17"/>
+        <v>4.2105565841438199</v>
+      </c>
+      <c r="W34" s="108">
+        <f t="shared" si="18"/>
+        <v>2.7223027750391986</v>
+      </c>
+      <c r="X34" s="112">
+        <f t="shared" si="19"/>
+        <v>14.605223716678891</v>
+      </c>
     </row>
-    <row r="35" spans="1:20" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="103" t="s">
+    <row r="35" spans="1:24" ht="15" customHeight="1" thickBot="1">
+      <c r="A35" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="104"/>
+      <c r="B35" s="117"/>
       <c r="C35" s="37">
         <f>SUM(C13:C34)</f>
         <v>25315.934758509604</v>
@@ -11012,11 +15899,11 @@
       <c r="F35" s="39"/>
       <c r="G35" s="40">
         <f>SUMIF(G13:G34,"&lt;&gt;TBD")</f>
-        <v>3775429054.2717938</v>
+        <v>4263701525.9110694</v>
       </c>
       <c r="H35" s="37">
         <f>SUMIF(H13:H34,"&lt;&gt;TBD")</f>
-        <v>3775.429054271794</v>
+        <v>4263.7015259110703</v>
       </c>
       <c r="I35" s="41"/>
       <c r="J35" s="46">
@@ -11059,35 +15946,51 @@
         <f t="shared" si="14"/>
         <v>485094372.87</v>
       </c>
-      <c r="T35" s="68">
+      <c r="T35" s="69">
         <f t="shared" si="15"/>
         <v>357018385.5</v>
       </c>
+      <c r="U35" s="109">
+        <f t="shared" si="16"/>
+        <v>664</v>
+      </c>
+      <c r="V35" s="110">
+        <f t="shared" si="17"/>
+        <v>364.4</v>
+      </c>
+      <c r="W35" s="110">
+        <f t="shared" si="18"/>
+        <v>235.6</v>
+      </c>
+      <c r="X35" s="112">
+        <f t="shared" si="19"/>
+        <v>1264</v>
+      </c>
     </row>
-    <row r="36" spans="1:20" ht="15" customHeight="1">
-      <c r="A36" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="108"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="108"/>
+    <row r="36" spans="1:24" ht="15" customHeight="1">
+      <c r="A36" s="121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="121"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="121"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="121"/>
+      <c r="H36" s="121"/>
       <c r="Q36" s="61"/>
       <c r="R36" s="61"/>
     </row>
-    <row r="38" spans="1:20" ht="15" customHeight="1">
-      <c r="A38" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="106"/>
-      <c r="C38" s="106"/>
-      <c r="D38" s="106"/>
-      <c r="E38" s="106"/>
+    <row r="38" spans="1:24" ht="15" customHeight="1">
+      <c r="A38" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="119"/>
+      <c r="C38" s="119"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="119"/>
     </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1">
+    <row r="39" spans="1:24" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
@@ -11098,13 +16001,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1">
+    <row r="40" spans="1:24" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>56</v>
       </c>
@@ -11120,33 +16023,33 @@
         <f>IFERROR(VLOOKUP(A40,$A$7:$D$9,4,FALSE()),"-")</f>
         <v>302000</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="102">
         <f>SUMIF($E$13:$E$34,A40,$H$13:$H$34)</f>
         <v>1778.8945325825241</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1">
+    <row r="41" spans="1:24" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="17">
         <f>COUNTIF($E$13:$E$34,A41)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" s="9">
         <f>SUMIF($E$13:$E$34,A41,$C$13:$C$34)</f>
-        <v>14120.467412390599</v>
+        <v>17713.347998404402</v>
       </c>
       <c r="D41" s="4">
         <f>IFERROR(VLOOKUP(A41,$A$7:$D$9,4,FALSE()),"-")</f>
         <v>135900</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="102">
         <f>SUMIF($E$13:$E$34,A41,$H$13:$H$34)</f>
-        <v>1918.9715213438828</v>
+        <v>2407.243992983158</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1">
+    <row r="42" spans="1:24" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>62</v>
       </c>
@@ -11162,31 +16065,31 @@
         <f>IFERROR(VLOOKUP(A42,$A$7:$D$9,4,FALSE()),"-")</f>
         <v>45300</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="102">
         <f>SUMIF($E$13:$E$34,A42,$H$13:$H$34)</f>
         <v>77.563000345386953</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1">
+    <row r="43" spans="1:24" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B43" s="17">
         <f>COUNTIF($E$13:$E$34,A43)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C43" s="9">
         <f>SUMIF($E$13:$E$34,A43,$C$13:$C$34)</f>
-        <v>3592.8805860138</v>
+        <v>0</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1">
+    <row r="44" spans="1:24" ht="15" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>27</v>
       </c>
@@ -11196,151 +16099,141 @@
       </c>
       <c r="C44" s="13">
         <f>SUM(C40:C43)</f>
-        <v>25315.934758509597</v>
+        <v>25315.934758509604</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="13">
         <f>SUMIF(E40:E43,"&lt;&gt;TBD")</f>
-        <v>3775.429054271794</v>
+        <v>4263.7015259110694</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1">
+    <row r="46" spans="1:24" ht="15" customHeight="1">
       <c r="A46" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1">
-      <c r="A47" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="B47" s="108"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="108"/>
-      <c r="E47" s="108"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="108"/>
+    <row r="47" spans="1:24" ht="15" customHeight="1">
+      <c r="A47" s="121" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="121"/>
+      <c r="C47" s="121"/>
+      <c r="D47" s="121"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="121"/>
+      <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="1:20" ht="15" customHeight="1">
-      <c r="A48" s="108" t="s">
-        <v>121</v>
-      </c>
-      <c r="B48" s="108"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="108"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="108"/>
+    <row r="48" spans="1:24" ht="15" customHeight="1">
+      <c r="A48" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="121"/>
+      <c r="C48" s="121"/>
+      <c r="D48" s="121"/>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="121"/>
+      <c r="H48" s="121"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
-      <c r="A49" s="108" t="s">
-        <v>122</v>
-      </c>
-      <c r="B49" s="108"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="108"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="108"/>
+      <c r="A49" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="121"/>
+      <c r="C49" s="121"/>
+      <c r="D49" s="121"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="121"/>
+      <c r="H49" s="121"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
-      <c r="A50" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="B50" s="108"/>
-      <c r="C50" s="108"/>
-      <c r="D50" s="108"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="108"/>
+      <c r="A50" s="121" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="121"/>
+      <c r="C50" s="121"/>
+      <c r="D50" s="121"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="121"/>
+      <c r="H50" s="121"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
-      <c r="A51" s="108" t="s">
-        <v>124</v>
-      </c>
-      <c r="B51" s="108"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="108"/>
-      <c r="E51" s="108"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="108"/>
+      <c r="A51" s="121" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="121"/>
+      <c r="C51" s="121"/>
+      <c r="D51" s="121"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="121"/>
+      <c r="H51" s="121"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
-      <c r="A52" s="108" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="108"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="108"/>
+      <c r="A52" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="121"/>
+      <c r="C52" s="121"/>
+      <c r="D52" s="121"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="121"/>
+      <c r="H52" s="121"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
-      <c r="A53" s="108" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="108"/>
-      <c r="C53" s="108"/>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="108"/>
-      <c r="H53" s="108"/>
+      <c r="A53" s="121" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" s="121"/>
+      <c r="C53" s="121"/>
+      <c r="D53" s="121"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="121"/>
+      <c r="H53" s="121"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
-      <c r="A54" s="108" t="s">
-        <v>127</v>
-      </c>
-      <c r="B54" s="108"/>
-      <c r="C54" s="108"/>
-      <c r="D54" s="108"/>
-      <c r="E54" s="108"/>
-      <c r="F54" s="108"/>
-      <c r="G54" s="108"/>
-      <c r="H54" s="108"/>
+      <c r="A54" s="121" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="121"/>
+      <c r="C54" s="121"/>
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="121"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
-      <c r="A55" s="108" t="s">
-        <v>128</v>
-      </c>
-      <c r="B55" s="108"/>
-      <c r="C55" s="108"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="108"/>
-      <c r="F55" s="108"/>
-      <c r="G55" s="108"/>
-      <c r="H55" s="108"/>
+      <c r="A55" s="121" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="121"/>
+      <c r="C55" s="121"/>
+      <c r="D55" s="121"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="121"/>
+      <c r="H55" s="121"/>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
-      <c r="A56" s="108" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" s="108"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="108"/>
-      <c r="H56" s="108"/>
+      <c r="A56" s="121" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" s="121"/>
+      <c r="C56" s="121"/>
+      <c r="D56" s="121"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="121"/>
+      <c r="H56" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A54:H54"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A56:H56"/>
@@ -11349,15 +16242,26 @@
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19B1645-907D-B343-92EE-D8D505DE27FA}">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="16.28515625" customWidth="1"/>
@@ -11372,69 +16276,79 @@
     <col min="19" max="20" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="75.95" thickBot="1">
+    <row r="1" spans="1:24" ht="75.95" thickBot="1">
       <c r="A1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D1" s="95" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F1" s="95" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G1" s="95" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I1" s="95" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="M1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="N1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="O1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="P1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="Q1" s="95" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="R1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="S1" s="94" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="T1" s="94" t="s">
-        <v>130</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="U1" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="V1" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="W1" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="X1" s="94"/>
     </row>
-    <row r="2" spans="1:20" ht="63.95">
+    <row r="2" spans="1:24" ht="63.95">
       <c r="A2" s="30" t="s">
         <v>14</v>
       </c>
@@ -11445,58 +16359,68 @@
         <v>19</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E2" s="71" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2" s="71" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H2" s="71" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I2" s="73" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J2" s="74" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K2" s="75" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="L2" s="76" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="M2" s="77" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N2" s="78" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O2" s="78" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="P2" s="78" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q2" s="79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R2" s="80" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="S2" s="81" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="T2" s="81" t="s">
-        <v>140</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="U2" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="V2" s="111" t="s">
+        <v>124</v>
+      </c>
+      <c r="W2" s="111" t="s">
+        <v>125</v>
+      </c>
+      <c r="X2" s="42"/>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:24">
       <c r="A3" s="82">
         <v>2070</v>
       </c>
@@ -11513,16 +16437,16 @@
         <v>62</v>
       </c>
       <c r="F3" s="87" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G3" s="87" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H3" s="84">
         <v>18.600000000000001</v>
       </c>
       <c r="I3" s="88" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J3" s="89">
         <v>20497.87</v>
@@ -11537,7 +16461,7 @@
         <v>4.83</v>
       </c>
       <c r="N3" s="97" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="O3" s="97">
         <v>16658.669999999998</v>
@@ -11546,7 +16470,7 @@
         <v>29261.86</v>
       </c>
       <c r="Q3" s="98" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="R3" s="99">
         <v>49498.8</v>
@@ -11557,14 +16481,24 @@
       <c r="T3" s="99">
         <v>5789590.6799999997</v>
       </c>
+      <c r="U3" s="106">
+        <v>10.767759775601675</v>
+      </c>
+      <c r="V3" s="106">
+        <v>5.9092946720320025</v>
+      </c>
+      <c r="W3" s="106">
+        <v>3.8206087396562567</v>
+      </c>
+      <c r="X3" s="106"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:24">
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
       <c r="S7" s="81"/>
       <c r="T7" s="81"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:24">
       <c r="P8" s="93"/>
       <c r="Q8" s="93"/>
       <c r="S8" s="93"/>
@@ -11587,10 +16521,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="32.1">
       <c r="A1" s="96" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2">
